--- a/output/ANANDRATHI_shareholder_categories.xlsx
+++ b/output/ANANDRATHI_shareholder_categories.xlsx
@@ -1049,6 +1049,11 @@
           <t>Azeez Family Trust</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n">
         <v>4207494</v>
       </c>
@@ -1073,25 +1078,37 @@
         <v>3365054</v>
       </c>
       <c r="O10" s="3" t="n"/>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="n"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>private_family_trust</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://trendlyne.com/equity/share-holding/747241/ANANDRATHI/31-03-2022/anand-rathi-wealth-ltd/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1285,6 +1302,11 @@
           <t>Echjay Industries Pvt Ltd</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n">
         <v>1683740</v>
       </c>
@@ -1309,25 +1331,37 @@
         <v>1675800</v>
       </c>
       <c r="O14" s="3" t="n"/>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="n"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://trendlyne.com/equity/share-holding/747241/ANANDRATHI/31-03-2022/anand-rathi-wealth-ltd/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1767,6 +1801,11 @@
           <t>Norges Bank</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Foreign Pension Fund</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="n">
         <v>897125</v>
       </c>
@@ -1793,23 +1832,39 @@
       <c r="O22" s="3" t="n"/>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
-      <c r="T22" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>pension_fund</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>pension_assets</t>
+        </is>
+      </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V22" s="4" t="n"/>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.investing.com/equities/anand-rathi-wealth-ownership</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4387,6 +4442,11 @@
           <t>Nomura Holdings Inc</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
@@ -4407,25 +4467,37 @@
         <v>9800</v>
       </c>
       <c r="O68" s="3" t="n"/>
-      <c r="P68" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n"/>
-      <c r="U68" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V68" s="4" t="n"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nomura_Holdings</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4436,6 +4508,11 @@
       <c r="B69" t="inlineStr">
         <is>
           <t>Nationwide Fund Advisors</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D69" s="3" t="n"/>
@@ -4454,25 +4531,37 @@
         <v>9682</v>
       </c>
       <c r="O69" s="3" t="n"/>
-      <c r="P69" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R69" s="4" t="n"/>
-      <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
-      <c r="U69" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V69" s="4" t="n"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>https://www.federalregister.gov/documents/2018/03/13/2018-05039/nationwide-fund-advisors-and-etf-series-solutions</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4899,6 +4988,11 @@
           <t>Angel One Ltd</t>
         </is>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D77" s="3" t="n">
         <v>252</v>
       </c>
@@ -4925,23 +5019,39 @@
       <c r="O77" s="3" t="n"/>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q77" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R77" s="4" t="n"/>
-      <c r="S77" s="4" t="n"/>
-      <c r="T77" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S77" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>custody_only</t>
+        </is>
+      </c>
       <c r="U77" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V77" s="4" t="n"/>
+      <c r="V77" s="4" t="inlineStr">
+        <is>
+          <t>https://inc42.com/buzz/angel-one-amc-gets-sebi-nod-to-start-mutual-fund-business</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5008,6 +5118,11 @@
           <t>Legal &amp; General Group PLC</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Foreign Insurance</t>
+        </is>
+      </c>
       <c r="D79" s="3" t="n">
         <v>4328</v>
       </c>
@@ -5032,25 +5147,37 @@
         <v>4328</v>
       </c>
       <c r="O79" s="3" t="n"/>
-      <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="n"/>
-      <c r="T79" s="4" t="n"/>
-      <c r="U79" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V79" s="4" t="n"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Legal_%26_General</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5061,6 +5188,11 @@
       <c r="B80" t="inlineStr">
         <is>
           <t>Franklin Templeton Inc</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D80" s="3" t="n"/>
@@ -5083,25 +5215,37 @@
         <v>3026</v>
       </c>
       <c r="O80" s="3" t="n"/>
-      <c r="P80" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R80" s="4" t="n"/>
-      <c r="S80" s="4" t="n"/>
-      <c r="T80" s="4" t="n"/>
-      <c r="U80" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V80" s="4" t="n"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>https://www.ipqwery.com/ipowner/en/owner/ip/485181-franklin-resources-inc.html</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5166,6 +5310,11 @@
           <t>FlexShares Trust</t>
         </is>
       </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D82" s="3" t="n">
         <v>3072</v>
       </c>
@@ -5190,25 +5339,37 @@
         <v>1476</v>
       </c>
       <c r="O82" s="3" t="n"/>
-      <c r="P82" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R82" s="4" t="n"/>
-      <c r="S82" s="4" t="n"/>
-      <c r="T82" s="4" t="n"/>
-      <c r="U82" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V82" s="4" t="n"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>exchange_traded_fund_trust</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>https://www.flexshares.com/us/en/individual/press</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5219,6 +5380,11 @@
       <c r="B83" t="inlineStr">
         <is>
           <t>Canadian Imperial Bank of Commerce</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D83" s="3" t="n"/>
@@ -5239,23 +5405,39 @@
       <c r="O83" s="3" t="n"/>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R83" s="4" t="n"/>
-      <c r="S83" s="4" t="n"/>
-      <c r="T83" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R83" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="S83" s="4" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="T83" s="4" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U83" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V83" s="4" t="n"/>
+      <c r="V83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.marketscreener.com/quote/stock/CANADIAN-IMPERIAL-BANK-OF-40530896/company-shareholders</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5324,6 +5506,11 @@
       <c r="B85" t="inlineStr">
         <is>
           <t>Credit Agricole Group</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D85" s="3" t="n"/>
@@ -5344,25 +5531,37 @@
         <v>190</v>
       </c>
       <c r="O85" s="3" t="n"/>
-      <c r="P85" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R85" s="4" t="n"/>
-      <c r="S85" s="4" t="n"/>
-      <c r="T85" s="4" t="n"/>
-      <c r="U85" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V85" s="4" t="n"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>https://about.amundi.com/article/credit-agricole-sa-has-entered-exclusive-negotiations-societe-generale</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5373,6 +5572,11 @@
       <c r="B86" t="inlineStr">
         <is>
           <t>Deutsche Bank AG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D86" s="3" t="n"/>
@@ -5397,25 +5601,37 @@
         <v>188</v>
       </c>
       <c r="O86" s="3" t="n"/>
-      <c r="P86" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R86" s="4" t="n"/>
-      <c r="S86" s="4" t="n"/>
-      <c r="T86" s="4" t="n"/>
-      <c r="U86" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V86" s="4" t="n"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/world/india/deutsche-banks-dws-buy-40-stake-nippon-life-india-asset-management-2025-11-13</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5475,6 +5691,11 @@
           <t>Prudential Financial Inc</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Foreign Insurance</t>
+        </is>
+      </c>
       <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="n"/>
       <c r="F88" s="3" t="n">
@@ -5497,23 +5718,39 @@
       <c r="O88" s="3" t="n"/>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q88" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R88" s="4" t="n"/>
-      <c r="S88" s="4" t="n"/>
-      <c r="T88" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R88" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S88" s="4" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T88" s="4" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U88" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V88" s="4" t="n"/>
+      <c r="V88" s="4" t="inlineStr">
+        <is>
+          <t>https://ad-hoc-news.de/boerse/news/ueberblick/prudential-financial-balances-insuran/69743267</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5524,6 +5761,11 @@
       <c r="B89" t="inlineStr">
         <is>
           <t>FIL Ltd</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D89" s="3" t="n"/>
@@ -5540,25 +5782,37 @@
         <v>0</v>
       </c>
       <c r="O89" s="3" t="n"/>
-      <c r="P89" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R89" s="4" t="n"/>
-      <c r="S89" s="4" t="n"/>
-      <c r="T89" s="4" t="n"/>
-      <c r="U89" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V89" s="4" t="n"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fidelity_International</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5569,6 +5823,11 @@
       <c r="B90" t="inlineStr">
         <is>
           <t>Russell Investments Group Ltd</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -5595,23 +5854,39 @@
       <c r="O90" s="3" t="n"/>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R90" s="4" t="n"/>
-      <c r="S90" s="4" t="n"/>
-      <c r="T90" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R90" s="4" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="S90" s="4" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T90" s="4" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U90" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V90" s="4" t="n"/>
+      <c r="V90" s="4" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12595999</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5942,6 +6217,11 @@
           <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D97" s="3" t="n"/>
       <c r="E97" s="3" t="n"/>
       <c r="F97" s="3" t="n">
@@ -5960,25 +6240,37 @@
         <v>0</v>
       </c>
       <c r="O97" s="3" t="n"/>
-      <c r="P97" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R97" s="4" t="n"/>
-      <c r="S97" s="4" t="n"/>
-      <c r="T97" s="4" t="n"/>
-      <c r="U97" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V97" s="4" t="n"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>https://jpmorganchaseco.gcs-web.com/static-files/3d1cfdc0-b391-4c71-a055-cb09f463622e</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5989,6 +6281,11 @@
       <c r="B98" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Foreign Insurance</t>
         </is>
       </c>
       <c r="D98" s="3" t="n"/>
@@ -6013,23 +6310,39 @@
       <c r="O98" s="3" t="n"/>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q98" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R98" s="4" t="n"/>
-      <c r="S98" s="4" t="n"/>
-      <c r="T98" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R98" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="S98" s="4" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T98" s="4" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U98" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V98" s="4" t="n"/>
+      <c r="V98" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sun_Life_Financial</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6096,6 +6409,11 @@
           <t>Rawal Family Trust</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
+        </is>
+      </c>
       <c r="D100" s="3" t="n">
         <v>1750352</v>
       </c>
@@ -6116,25 +6434,37 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n"/>
-      <c r="P100" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R100" s="4" t="n"/>
-      <c r="S100" s="4" t="n"/>
-      <c r="T100" s="4" t="n"/>
-      <c r="U100" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V100" s="4" t="n"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>private_family_trust</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>https://trendlyne.com/equity/share-holding/747241/ANANDRATHI/31-03-2022/anand-rathi-wealth-ltd/</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6145,6 +6475,11 @@
       <c r="B101" t="inlineStr">
         <is>
           <t>SUHAS GUPTA FAMILY TRUST</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
@@ -6171,25 +6506,37 @@
         <v>0</v>
       </c>
       <c r="O101" s="3" t="n"/>
-      <c r="P101" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R101" s="4" t="n"/>
-      <c r="S101" s="4" t="n"/>
-      <c r="T101" s="4" t="n"/>
-      <c r="U101" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V101" s="4" t="n"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>private_family_trust</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>https://trendlyne.com/equity/share-holding/747241/ANANDRATHI/31-03-2022/anand-rathi-wealth-ltd/</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6200,6 +6547,11 @@
       <c r="B102" t="inlineStr">
         <is>
           <t>Munix India Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
@@ -6226,25 +6578,37 @@
         <v>0</v>
       </c>
       <c r="O102" s="3" t="n"/>
-      <c r="P102" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R102" s="4" t="n"/>
-      <c r="S102" s="4" t="n"/>
-      <c r="T102" s="4" t="n"/>
-      <c r="U102" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V102" s="4" t="n"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>https://www.tofler.in/munix-india-private-limited/company/U00000PB2003PTC025986</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6255,6 +6619,11 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>ANANDRATHI HOUSING FIN LTD</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
@@ -6275,25 +6644,37 @@
         <v>0</v>
       </c>
       <c r="O103" s="3" t="n"/>
-      <c r="P103" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R103" s="4" t="n"/>
-      <c r="S103" s="4" t="n"/>
-      <c r="T103" s="4" t="n"/>
-      <c r="U103" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V103" s="4" t="n"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>operating_company</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>operating_company_treasury</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/company/anandrathi-housing-finance-limited/U67100MH2018PLC304174</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6304,6 +6685,11 @@
       <c r="B104" t="inlineStr">
         <is>
           <t>Wilshire Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D104" s="3" t="n"/>
@@ -6320,25 +6706,37 @@
         <v>0</v>
       </c>
       <c r="O104" s="3" t="n"/>
-      <c r="P104" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R104" s="4" t="n"/>
-      <c r="S104" s="4" t="n"/>
-      <c r="T104" s="4" t="n"/>
-      <c r="U104" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V104" s="4" t="n"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>https://www.wilshire.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/output/ANANDRATHI_shareholder_categories.xlsx
+++ b/output/ANANDRATHI_shareholder_categories.xlsx
@@ -852,10 +852,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -932,6 +942,11 @@
           <t>Vanguard Group Inc/The</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n">
         <v>2751420</v>
       </c>
@@ -956,25 +971,37 @@
         <v>4361760</v>
       </c>
       <c r="O8" s="3" t="n"/>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n"/>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="n"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q849363</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1031,10 +1058,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -1374,6 +1411,11 @@
           <t>Blackrock Inc</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="n">
         <v>1154273</v>
       </c>
@@ -1398,25 +1440,37 @@
         <v>1624259</v>
       </c>
       <c r="O15" s="3" t="n"/>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="n"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1364742/000119312508041884/d10k.htm</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1473,10 +1527,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -1535,10 +1599,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -1597,10 +1671,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -1659,10 +1743,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -1921,10 +2015,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2041,10 +2145,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2227,10 +2341,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2289,10 +2413,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2351,10 +2485,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2409,10 +2553,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2471,10 +2625,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2525,10 +2689,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2541,6 +2715,11 @@
       <c r="B34" t="inlineStr">
         <is>
           <t>Mirae Asset Financial Group</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -2567,25 +2746,37 @@
         <v>175463</v>
       </c>
       <c r="O34" s="3" t="n"/>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
-      <c r="U34" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V34" s="4" t="n"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mirae_Asset_Financial_Group</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2596,6 +2787,11 @@
       <c r="B35" t="inlineStr">
         <is>
           <t>American Century Cos Inc</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -2622,25 +2818,37 @@
         <v>173687</v>
       </c>
       <c r="O35" s="3" t="n"/>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R35" s="4" t="n"/>
-      <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="n"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/American_Century_Investments</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2651,6 +2859,11 @@
       <c r="B36" t="inlineStr">
         <is>
           <t>Goldman Sachs Group Inc/The</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -2677,25 +2890,37 @@
         <v>169570</v>
       </c>
       <c r="O36" s="3" t="n"/>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
-      <c r="U36" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V36" s="4" t="n"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://www.gsam.com/content/dam/gsam/pdfs/international/en/fund-literature/monthly-factsheet-goldman-sachs-india-equity-portfolio-class-i-shares.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2706,6 +2931,11 @@
       <c r="B37" t="inlineStr">
         <is>
           <t>Trust Investment Advisors Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Domestic corporate</t>
         </is>
       </c>
       <c r="D37" s="3" t="n"/>
@@ -2726,23 +2956,39 @@
       <c r="O37" s="3" t="n"/>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R37" s="4" t="n"/>
-      <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
       <c r="U37" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V37" s="4" t="n"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.trustgroup.in/</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2799,10 +3045,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2861,10 +3117,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2921,10 +3187,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -2937,6 +3213,11 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>WBC Holdings LP</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D41" s="3" t="n"/>
@@ -2955,25 +3236,37 @@
         <v>139600</v>
       </c>
       <c r="O41" s="3" t="n"/>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R41" s="4" t="n"/>
-      <c r="S41" s="4" t="n"/>
-      <c r="T41" s="4" t="n"/>
-      <c r="U41" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V41" s="4" t="n"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/profile/company/1307537D:US</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3030,10 +3323,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3046,6 +3349,11 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>Victory Capital Management Inc</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -3068,25 +3376,37 @@
         <v>126480</v>
       </c>
       <c r="O43" s="3" t="n"/>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R43" s="4" t="n"/>
-      <c r="S43" s="4" t="n"/>
-      <c r="T43" s="4" t="n"/>
-      <c r="U43" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V43" s="4" t="n"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Victory_Capital</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3097,6 +3417,11 @@
       <c r="B44" t="inlineStr">
         <is>
           <t>Driehaus Capital Management LLC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -3121,25 +3446,37 @@
         <v>121650</v>
       </c>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R44" s="4" t="n"/>
-      <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n"/>
-      <c r="U44" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V44" s="4" t="n"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://www.cbinsights.com/company/driehaus-capital-management</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3188,10 +3525,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3264,6 +3611,11 @@
           <t>WisdomTree Inc</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="n">
         <v>111362</v>
       </c>
@@ -3288,25 +3640,37 @@
         <v>90460</v>
       </c>
       <c r="O47" s="3" t="n"/>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R47" s="4" t="n"/>
-      <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
-      <c r="U47" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V47" s="4" t="n"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/WisdomTree_Investments</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3363,10 +3727,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3425,10 +3799,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3485,10 +3869,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3501,6 +3895,11 @@
       <c r="B51" t="inlineStr">
         <is>
           <t>Teachers Insurance &amp; Annuity Association of America</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Foreign Pension Fund</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
@@ -3529,23 +3928,39 @@
       <c r="O51" s="3" t="n"/>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R51" s="4" t="n"/>
-      <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>pension_fund</t>
+        </is>
+      </c>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>pension_assets</t>
+        </is>
+      </c>
       <c r="U51" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V51" s="4" t="n"/>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tiaa.org/public/about-tiaa</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3594,10 +4009,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3610,6 +4035,11 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>State Street Corp</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
@@ -3636,25 +4066,37 @@
         <v>51736</v>
       </c>
       <c r="O53" s="3" t="n"/>
-      <c r="P53" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R53" s="4" t="n"/>
-      <c r="S53" s="4" t="n"/>
-      <c r="T53" s="4" t="n"/>
-      <c r="U53" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V53" s="4" t="n"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>https://money.usnews.com/funds/spdr/state-street-global-advisors/overview</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3701,10 +4143,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3717,6 +4169,11 @@
       <c r="B55" t="inlineStr">
         <is>
           <t>FMR LLC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
@@ -3743,25 +4200,37 @@
         <v>49939</v>
       </c>
       <c r="O55" s="3" t="n"/>
-      <c r="P55" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R55" s="4" t="n"/>
-      <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n"/>
-      <c r="U55" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V55" s="4" t="n"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>https://www.wikicorporates.org/wiki/Fidelity_Group</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3816,10 +4285,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3832,6 +4311,11 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>AllianceBernstein Holding LP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D57" s="3" t="n"/>
@@ -3850,25 +4334,37 @@
         <v>46870</v>
       </c>
       <c r="O57" s="3" t="n"/>
-      <c r="P57" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R57" s="4" t="n"/>
-      <c r="S57" s="4" t="n"/>
-      <c r="T57" s="4" t="n"/>
-      <c r="U57" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V57" s="4" t="n"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://alliancebernsteinholdinglp.gcs-web.com/static-files/4a5bd53f-3daf-46c2-b7ed-58fd389cd163.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3917,10 +4413,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -3995,6 +4501,11 @@
       <c r="B60" t="inlineStr">
         <is>
           <t>National Bank of Canada</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Foreign AMC</t>
         </is>
       </c>
       <c r="D60" s="3" t="n"/>
@@ -4015,23 +4526,39 @@
       <c r="O60" s="3" t="n"/>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>web</t>
         </is>
       </c>
       <c r="Q60" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R60" s="4" t="n"/>
-      <c r="S60" s="4" t="n"/>
-      <c r="T60" s="4" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R60" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U60" s="4" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="V60" s="4" t="n"/>
+      <c r="V60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nbc.ca/wealth-management/trust/institutional-services.html</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4042,6 +4569,11 @@
       <c r="B61" t="inlineStr">
         <is>
           <t>Thrivent Financial for Lutherans</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Foreign Insurance</t>
         </is>
       </c>
       <c r="D61" s="3" t="n"/>
@@ -4062,25 +4594,37 @@
         <v>36551</v>
       </c>
       <c r="O61" s="3" t="n"/>
-      <c r="P61" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R61" s="4" t="n"/>
-      <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
-      <c r="U61" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V61" s="4" t="n"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Thrivent</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4137,10 +4681,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4215,6 +4769,11 @@
       <c r="B64" t="inlineStr">
         <is>
           <t>Taiwan Securities Co Ltd</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Foreign corporate</t>
         </is>
       </c>
       <c r="D64" s="3" t="n"/>
@@ -4235,25 +4794,37 @@
         <v>17993</v>
       </c>
       <c r="O64" s="3" t="n"/>
-      <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="R64" s="4" t="n"/>
-      <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n"/>
-      <c r="U64" s="4" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-      <c r="V64" s="4" t="n"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>own_balance_sheet</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/profile/company/6010:TT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4370,10 +4941,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4424,10 +5005,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4614,10 +5205,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4730,10 +5331,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4788,10 +5399,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4846,10 +5467,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -4908,10 +5539,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -5100,10 +5741,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -5292,10 +5943,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -5490,10 +6151,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>insurer</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>insurance_float</t>
+        </is>
+      </c>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
@@ -5531,35 +6202,39 @@
         <v>190</v>
       </c>
       <c r="O85" s="3" t="n"/>
-      <c r="P85" t="inlineStr">
+      <c r="P85" s="4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R85" s="4" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S85" s="4" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T85" s="4" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>https://about.amundi.com/article/credit-agricole-sa-has-entered-exclusive-negotiations-societe-generale</t>
+      <c r="U85" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="V85" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Amundi</t>
         </is>
       </c>
     </row>
@@ -5601,35 +6276,39 @@
         <v>188</v>
       </c>
       <c r="O86" s="3" t="n"/>
-      <c r="P86" t="inlineStr">
+      <c r="P86" s="4" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R86" s="4" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S86" s="4" t="inlineStr">
         <is>
           <t>bank</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T86" s="4" t="inlineStr">
         <is>
           <t>managed_funds</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>https://www.reuters.com/world/india/deutsche-banks-dws-buy-40-stake-nippon-life-india-asset-management-2025-11-13</t>
+      <c r="U86" s="4" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="V86" s="4" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/DWS_Group</t>
         </is>
       </c>
     </row>
@@ -6391,10 +7070,20 @@
           <t>IN</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>asset_manager</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>managed_funds</t>
+        </is>
+      </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>deterministic rule</t>
+          <t>matched by deterministic name rule</t>
         </is>
       </c>
     </row>
